--- a/forms/trg/Formulir_TRG_ecohealth.xlsx
+++ b/forms/trg/Formulir_TRG_ecohealth.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B20)</f>
+        <f>COUNTA(Anggota!B5:B21)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F20)</f>
+        <f>COUNTA(Anggota!F5:F21)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,18 +913,18 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Muh Fajaruddin Natsir, S.KM., M.Kes.</t>
+          <t>Prof. Anwar, S.KM, M.Kes., Ph.D</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Instansi xxxxx</t>
+          <t>; Instansi xxxxx</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -946,18 +946,18 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Basir, SKM., M.Sc</t>
+          <t>Muh Fajaruddin Natsir, S.KM., M.Kes.</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="12" t="n"/>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Instansi</t>
+          <t>Instansi xxxxx</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -979,12 +979,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Dr Owildan Wisudawan B. SKM M.Kes.</t>
+          <t>Basir, SKM., M.Sc</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="12" t="n"/>
@@ -1012,22 +1012,18 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Wesam AL Madhoun</t>
+          <t>Dr Owildan Wisudawan B. SKM M.Kes.</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
-        <is>
-          <t>Gaza University</t>
-        </is>
-      </c>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="n"/>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Global Ambassadors of Sustainability</t>
+          <t>Instansi</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1047,10 +1043,26 @@
       <c r="A9" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="12" t="n"/>
-      <c r="C9" s="12" t="n"/>
-      <c r="D9" s="12" t="n"/>
-      <c r="E9" s="11" t="n"/>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>Wesam AL Madhoun</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>External collaborator</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>Gaza University</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>Global Ambassadors of Sustainability</t>
+        </is>
+      </c>
       <c r="F9" s="12" t="n"/>
       <c r="G9" s="12" t="n"/>
       <c r="H9" s="12" t="n"/>
@@ -1058,7 +1070,11 @@
       <c r="J9" s="12" t="n"/>
       <c r="K9" s="12" t="n"/>
       <c r="L9" s="12" t="n"/>
-      <c r="M9" s="12" t="n"/>
+      <c r="M9" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -1247,15 +1263,32 @@
       <c r="L20" s="12" t="n"/>
       <c r="M20" s="12" t="n"/>
     </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="12" t="n"/>
+      <c r="C21" s="12" t="n"/>
+      <c r="D21" s="12" t="n"/>
+      <c r="E21" s="11" t="n"/>
+      <c r="F21" s="12" t="n"/>
+      <c r="G21" s="12" t="n"/>
+      <c r="H21" s="12" t="n"/>
+      <c r="I21" s="12" t="n"/>
+      <c r="J21" s="12" t="n"/>
+      <c r="K21" s="12" t="n"/>
+      <c r="L21" s="12" t="n"/>
+      <c r="M21" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
